--- a/docs/eu/StructureDefinition-Ratio-uv-ips.xlsx
+++ b/docs/eu/StructureDefinition-Ratio-uv-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T17:10:39+02:00</t>
+    <t>2026-03-15T18:11:06+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/eu/StructureDefinition-Ratio-uv-ips.xlsx
+++ b/docs/eu/StructureDefinition-Ratio-uv-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T18:11:06+02:00</t>
+    <t>2026-03-15T21:22:52+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
